--- a/12625004.xlsx
+++ b/12625004.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0eb0b81235d0062c/Desktop/776/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="149" documentId="8_{E03027F0-8265-43BF-A0A2-E202A7C3F2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28FDDE51-F349-495D-9ADA-2267F3FFC65C}"/>
+  <xr:revisionPtr revIDLastSave="200" documentId="8_{E03027F0-8265-43BF-A0A2-E202A7C3F2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DF7324C-E42F-4032-A17B-1BDBB93FB448}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>I feltl good because today was my ca gone well</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> felt stresed</t>
   </si>
 </sst>
 </file>
@@ -2059,92 +2062,187 @@
       </c>
     </row>
     <row r="25" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B25" s="14">
+        <v>480</v>
+      </c>
+      <c r="C25" s="14">
+        <v>100</v>
+      </c>
+      <c r="D25" s="14">
+        <v>180</v>
+      </c>
+      <c r="E25" s="14">
+        <v>60</v>
+      </c>
+      <c r="F25" s="14">
+        <v>350</v>
+      </c>
+      <c r="G25" s="14">
+        <v>7</v>
+      </c>
+      <c r="H25" s="14">
+        <v>120</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="26" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B26" s="14">
+        <v>480</v>
+      </c>
+      <c r="C26" s="14">
+        <v>120</v>
+      </c>
+      <c r="D26" s="14">
+        <v>180</v>
+      </c>
+      <c r="E26" s="14">
+        <v>60</v>
+      </c>
+      <c r="F26" s="14">
+        <v>50</v>
+      </c>
+      <c r="G26" s="14">
+        <v>1</v>
+      </c>
+      <c r="H26" s="14">
+        <v>130</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="27" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B27" s="14">
+        <v>480</v>
+      </c>
+      <c r="C27" s="14">
+        <v>120</v>
+      </c>
+      <c r="D27" s="14">
+        <v>180</v>
+      </c>
+      <c r="E27" s="14">
+        <v>60</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <v>120</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="28" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B28" s="14">
+        <v>480</v>
+      </c>
+      <c r="C28" s="14">
+        <v>120</v>
+      </c>
+      <c r="D28" s="14">
+        <v>180</v>
+      </c>
+      <c r="E28" s="14">
+        <v>60</v>
+      </c>
+      <c r="F28" s="14">
+        <v>150</v>
+      </c>
+      <c r="G28" s="14">
+        <v>3</v>
+      </c>
+      <c r="H28" s="14">
+        <v>120</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>1110</v>
+      </c>
+      <c r="J28" s="15">
+        <v>120</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="29" spans="1:184" x14ac:dyDescent="0.35">
       <c r="A29" s="13"/>

--- a/12625004.xlsx
+++ b/12625004.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0eb0b81235d0062c/Desktop/776/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0eb0b81235d0062c/Documents/GitHub/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="200" documentId="8_{E03027F0-8265-43BF-A0A2-E202A7C3F2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DF7324C-E42F-4032-A17B-1BDBB93FB448}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{E03027F0-8265-43BF-A0A2-E202A7C3F2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA8AA60F-CC41-4443-9024-281349DFFE5D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,43 +232,13 @@
     <t>I am feeling relaxed</t>
   </si>
   <si>
-    <t>felt bit nervous</t>
-  </si>
-  <si>
-    <t>felt sad</t>
-  </si>
-  <si>
-    <t>felt little happy</t>
-  </si>
-  <si>
-    <t>today went well so I feel relived</t>
-  </si>
-  <si>
-    <t>felt stressed</t>
-  </si>
-  <si>
-    <t>felt relaxed</t>
-  </si>
-  <si>
-    <t>felt happy</t>
-  </si>
-  <si>
-    <t>2026--08-31</t>
-  </si>
-  <si>
-    <t>averge</t>
-  </si>
-  <si>
-    <t>I felt very nervous because today was my CA and I can not perform well</t>
+    <t>2026-08025</t>
   </si>
   <si>
     <t>high</t>
   </si>
   <si>
-    <t>I feltl good because today was my ca gone well</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> felt stresed</t>
+    <t>I felt good</t>
   </si>
 </sst>
 </file>
@@ -414,7 +384,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -458,7 +428,6 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -961,75 +930,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="21">
         <v>12625004</v>
       </c>
-      <c r="G2" s="22"/>
-      <c r="I2" s="19"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="22"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="42" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -1410,280 +1378,160 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13">
-        <v>46259</v>
+      <c r="A14" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="B14" s="14">
-        <v>540</v>
+        <v>350</v>
       </c>
       <c r="C14" s="14">
         <v>30</v>
       </c>
       <c r="D14" s="14">
+        <v>240</v>
+      </c>
+      <c r="E14" s="14">
+        <v>120</v>
+      </c>
+      <c r="F14" s="14">
         <v>350</v>
       </c>
-      <c r="E14" s="14">
-        <v>60</v>
-      </c>
-      <c r="F14" s="14">
-        <v>120</v>
-      </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H14" s="14">
         <v>120</v>
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>1220</v>
+        <v>1210</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="L14" s="16" t="s">
         <v>55</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="13">
-        <v>46260</v>
-      </c>
-      <c r="B15" s="14">
-        <v>540</v>
-      </c>
-      <c r="C15" s="14">
-        <v>30</v>
-      </c>
-      <c r="D15" s="14">
-        <v>240</v>
-      </c>
-      <c r="E15" s="14">
-        <v>60</v>
-      </c>
-      <c r="F15" s="14">
-        <v>350</v>
-      </c>
-      <c r="G15" s="14">
-        <v>7</v>
-      </c>
-      <c r="H15" s="14">
-        <v>120</v>
-      </c>
-      <c r="I15" s="15">
+      <c r="A15" s="13"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1340</v>
-      </c>
-      <c r="J15" s="15">
+        <v/>
+      </c>
+      <c r="J15" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="K15" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L15" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="M15" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="N15" s="17" t="s">
-        <v>67</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="13">
-        <v>46261</v>
-      </c>
-      <c r="B16" s="14">
-        <v>540</v>
-      </c>
-      <c r="C16" s="14">
-        <v>30</v>
-      </c>
-      <c r="D16" s="14">
-        <v>240</v>
-      </c>
-      <c r="E16" s="14">
-        <v>120</v>
-      </c>
-      <c r="F16" s="14">
-        <v>0</v>
-      </c>
-      <c r="G16" s="14">
-        <v>0</v>
-      </c>
-      <c r="H16" s="14">
-        <v>60</v>
-      </c>
-      <c r="I16" s="15">
+      <c r="A16" s="13"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>990</v>
-      </c>
-      <c r="J16" s="15">
+        <v/>
+      </c>
+      <c r="J16" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>450</v>
-      </c>
-      <c r="K16" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L16" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="M16" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>66</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A17" s="13">
-        <v>46262</v>
-      </c>
-      <c r="B17" s="14">
-        <v>480</v>
-      </c>
-      <c r="C17" s="14">
-        <v>60</v>
-      </c>
-      <c r="D17" s="14">
-        <v>180</v>
-      </c>
-      <c r="E17" s="14">
-        <v>70</v>
-      </c>
-      <c r="F17" s="14">
-        <v>110</v>
-      </c>
-      <c r="G17" s="14">
-        <v>0</v>
-      </c>
-      <c r="H17" s="14">
-        <v>120</v>
-      </c>
-      <c r="I17" s="15">
+      <c r="A17" s="13"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1020</v>
-      </c>
-      <c r="J17" s="15">
+        <v/>
+      </c>
+      <c r="J17" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>420</v>
-      </c>
-      <c r="K17" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L17" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M17" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>68</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A18" s="13">
-        <v>46263</v>
-      </c>
-      <c r="B18" s="14">
-        <v>480</v>
-      </c>
-      <c r="C18" s="14">
-        <v>60</v>
-      </c>
-      <c r="D18" s="14">
-        <v>180</v>
-      </c>
-      <c r="E18" s="14">
-        <v>120</v>
-      </c>
-      <c r="F18" s="14">
-        <v>0</v>
-      </c>
-      <c r="G18" s="14">
-        <v>0</v>
-      </c>
-      <c r="H18" s="14">
-        <v>20</v>
-      </c>
-      <c r="I18" s="15">
+      <c r="A18" s="13"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>860</v>
-      </c>
-      <c r="J18" s="15">
+        <v/>
+      </c>
+      <c r="J18" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>580</v>
-      </c>
-      <c r="K18" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L18" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M18" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>69</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A19" s="13">
-        <v>46264</v>
-      </c>
-      <c r="B19" s="14">
-        <v>480</v>
-      </c>
-      <c r="C19" s="14">
-        <v>60</v>
-      </c>
-      <c r="D19" s="14">
-        <v>180</v>
-      </c>
-      <c r="E19" s="14">
-        <v>60</v>
-      </c>
-      <c r="F19" s="14">
-        <v>0</v>
-      </c>
-      <c r="G19" s="14">
-        <v>0</v>
-      </c>
-      <c r="H19" s="14">
-        <v>60</v>
-      </c>
-      <c r="I19" s="15">
+      <c r="A19" s="13"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>840</v>
-      </c>
-      <c r="J19" s="15">
+        <v/>
+      </c>
+      <c r="J19" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>600</v>
-      </c>
-      <c r="K19" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L19" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="M19" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>70</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:184" x14ac:dyDescent="0.35">
       <c r="A20" s="13"/>
@@ -1694,14 +1542,8 @@
       <c r="F20" s="13"/>
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
-      <c r="I20" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
       <c r="K20" s="13"/>
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
@@ -1878,371 +1720,180 @@
       <c r="GB20" s="13"/>
     </row>
     <row r="21" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A21" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="B21" s="14">
-        <v>480</v>
-      </c>
-      <c r="C21" s="14">
-        <v>60</v>
-      </c>
-      <c r="D21" s="14">
-        <v>180</v>
-      </c>
-      <c r="E21" s="14">
-        <v>60</v>
-      </c>
-      <c r="F21" s="14">
-        <v>100</v>
-      </c>
-      <c r="G21" s="14">
-        <v>2</v>
-      </c>
-      <c r="H21" s="14">
-        <v>60</v>
-      </c>
-      <c r="I21" s="15">
+      <c r="A21" s="13"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>940</v>
-      </c>
-      <c r="J21" s="15">
+        <v/>
+      </c>
+      <c r="J21" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="K21" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L21" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="M21" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N21" s="17" t="s">
-        <v>71</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A22" s="13">
-        <v>46266</v>
-      </c>
-      <c r="B22" s="14">
-        <v>480</v>
-      </c>
-      <c r="C22" s="14">
-        <v>60</v>
-      </c>
-      <c r="D22" s="14">
-        <v>240</v>
-      </c>
-      <c r="E22" s="14">
-        <v>120</v>
-      </c>
-      <c r="F22" s="14">
-        <v>350</v>
-      </c>
-      <c r="G22" s="14">
-        <v>7</v>
-      </c>
-      <c r="H22" s="14">
-        <v>120</v>
-      </c>
-      <c r="I22" s="15">
+      <c r="A22" s="13"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1370</v>
-      </c>
-      <c r="J22" s="15">
+        <v/>
+      </c>
+      <c r="J22" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>70</v>
-      </c>
-      <c r="K22" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L22" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="M22" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N22" s="17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:184" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="13">
-        <v>46267</v>
-      </c>
-      <c r="B23" s="14">
-        <v>480</v>
-      </c>
-      <c r="C23" s="14">
-        <v>60</v>
-      </c>
-      <c r="D23" s="14">
-        <v>180</v>
-      </c>
-      <c r="E23" s="14">
-        <v>60</v>
-      </c>
-      <c r="F23" s="14">
-        <v>200</v>
-      </c>
-      <c r="G23" s="14">
-        <v>4</v>
-      </c>
-      <c r="H23" s="14">
-        <v>120</v>
-      </c>
-      <c r="I23" s="15">
+        <v/>
+      </c>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="17"/>
+    </row>
+    <row r="23" spans="1:184" x14ac:dyDescent="0.35">
+      <c r="A23" s="13"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1100</v>
-      </c>
-      <c r="J23" s="15">
+        <v/>
+      </c>
+      <c r="J23" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>340</v>
-      </c>
-      <c r="K23" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L23" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M23" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="N23" s="17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="24" spans="1:184" ht="29" x14ac:dyDescent="0.35">
-      <c r="A24" s="13">
-        <v>46268</v>
-      </c>
-      <c r="B24" s="14">
-        <v>480</v>
-      </c>
-      <c r="C24" s="14">
-        <v>60</v>
-      </c>
-      <c r="D24" s="14">
-        <v>180</v>
-      </c>
-      <c r="E24" s="14">
-        <v>60</v>
-      </c>
-      <c r="F24" s="14">
-        <v>350</v>
-      </c>
-      <c r="G24" s="14">
-        <v>7</v>
-      </c>
-      <c r="H24" s="14">
-        <v>120</v>
-      </c>
-      <c r="I24" s="15">
+        <v/>
+      </c>
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="16"/>
+      <c r="N23" s="17"/>
+    </row>
+    <row r="24" spans="1:184" x14ac:dyDescent="0.35">
+      <c r="A24" s="13"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1250</v>
-      </c>
-      <c r="J24" s="15">
+        <v/>
+      </c>
+      <c r="J24" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>190</v>
-      </c>
-      <c r="K24" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L24" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="M24" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="N24" s="17" t="s">
-        <v>76</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
+      <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A25" s="13">
-        <v>46269</v>
-      </c>
-      <c r="B25" s="14">
-        <v>480</v>
-      </c>
-      <c r="C25" s="14">
-        <v>100</v>
-      </c>
-      <c r="D25" s="14">
-        <v>180</v>
-      </c>
-      <c r="E25" s="14">
-        <v>60</v>
-      </c>
-      <c r="F25" s="14">
-        <v>350</v>
-      </c>
-      <c r="G25" s="14">
-        <v>7</v>
-      </c>
-      <c r="H25" s="14">
-        <v>120</v>
-      </c>
-      <c r="I25" s="15">
+      <c r="A25" s="13"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1290</v>
-      </c>
-      <c r="J25" s="15">
+        <v/>
+      </c>
+      <c r="J25" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>150</v>
-      </c>
-      <c r="K25" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L25" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="M25" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="N25" s="17" t="s">
-        <v>71</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="16"/>
+      <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A26" s="13">
-        <v>46270</v>
-      </c>
-      <c r="B26" s="14">
-        <v>480</v>
-      </c>
-      <c r="C26" s="14">
-        <v>120</v>
-      </c>
-      <c r="D26" s="14">
-        <v>180</v>
-      </c>
-      <c r="E26" s="14">
-        <v>60</v>
-      </c>
-      <c r="F26" s="14">
-        <v>50</v>
-      </c>
-      <c r="G26" s="14">
-        <v>1</v>
-      </c>
-      <c r="H26" s="14">
-        <v>130</v>
-      </c>
-      <c r="I26" s="15">
+      <c r="A26" s="13"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1020</v>
-      </c>
-      <c r="J26" s="15">
+        <v/>
+      </c>
+      <c r="J26" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>420</v>
-      </c>
-      <c r="K26" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L26" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M26" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N26" s="17" t="s">
-        <v>69</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
+      <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A27" s="13">
-        <v>46271</v>
-      </c>
-      <c r="B27" s="14">
-        <v>480</v>
-      </c>
-      <c r="C27" s="14">
-        <v>120</v>
-      </c>
-      <c r="D27" s="14">
-        <v>180</v>
-      </c>
-      <c r="E27" s="14">
-        <v>60</v>
-      </c>
-      <c r="F27" s="14">
-        <v>0</v>
-      </c>
-      <c r="G27" s="14">
-        <v>0</v>
-      </c>
-      <c r="H27" s="14">
-        <v>120</v>
-      </c>
-      <c r="I27" s="15">
+      <c r="A27" s="13"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>960</v>
-      </c>
-      <c r="J27" s="15">
+        <v/>
+      </c>
+      <c r="J27" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>480</v>
-      </c>
-      <c r="K27" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L27" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M27" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N27" s="17" t="s">
-        <v>69</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
+      <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A28" s="13">
-        <v>46272</v>
-      </c>
-      <c r="B28" s="14">
-        <v>480</v>
-      </c>
-      <c r="C28" s="14">
-        <v>120</v>
-      </c>
-      <c r="D28" s="14">
-        <v>180</v>
-      </c>
-      <c r="E28" s="14">
-        <v>60</v>
-      </c>
-      <c r="F28" s="14">
-        <v>150</v>
-      </c>
-      <c r="G28" s="14">
-        <v>3</v>
-      </c>
-      <c r="H28" s="14">
-        <v>120</v>
-      </c>
-      <c r="I28" s="15">
+      <c r="A28" s="13"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1110</v>
-      </c>
-      <c r="J28" s="15">
-        <v>120</v>
-      </c>
-      <c r="K28" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L28" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="M28" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="N28" s="17" t="s">
-        <v>77</v>
-      </c>
+        <v/>
+      </c>
+      <c r="J28" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:184" x14ac:dyDescent="0.35">
       <c r="A29" s="13"/>
@@ -10484,6 +10135,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/12625004.xlsx
+++ b/12625004.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0eb0b81235d0062c/Documents/GitHub/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0eb0b81235d0062c/Desktop/776/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{E03027F0-8265-43BF-A0A2-E202A7C3F2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA8AA60F-CC41-4443-9024-281349DFFE5D}"/>
+  <xr:revisionPtr revIDLastSave="397" documentId="8_{E03027F0-8265-43BF-A0A2-E202A7C3F2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9CA3ACA-7E2A-45B8-9059-8D7C73439ACE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,13 +232,76 @@
     <t>I am feeling relaxed</t>
   </si>
   <si>
-    <t>2026-08025</t>
+    <t>felt bit nervous</t>
+  </si>
+  <si>
+    <t>felt sad</t>
+  </si>
+  <si>
+    <t>felt little happy</t>
+  </si>
+  <si>
+    <t>today went well so I feel relived</t>
+  </si>
+  <si>
+    <t>felt stressed</t>
+  </si>
+  <si>
+    <t>felt relaxed</t>
+  </si>
+  <si>
+    <t>felt happy</t>
+  </si>
+  <si>
+    <t>2026--08-31</t>
+  </si>
+  <si>
+    <t>averge</t>
+  </si>
+  <si>
+    <t>I felt very nervous because today was my CA and I can not perform well</t>
   </si>
   <si>
     <t>high</t>
   </si>
   <si>
-    <t>I felt good</t>
+    <t>I feltl good because today was my ca gone well</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> felt stresed</t>
+  </si>
+  <si>
+    <t>averrage</t>
+  </si>
+  <si>
+    <t>today went very relaxed mood</t>
+  </si>
+  <si>
+    <t>`180</t>
+  </si>
+  <si>
+    <t>bad</t>
+  </si>
+  <si>
+    <t>felt happy to learn soomthing new</t>
+  </si>
+  <si>
+    <t>selt relaxed</t>
+  </si>
+  <si>
+    <t>HAPPY</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>FELT HAPPY</t>
+  </si>
+  <si>
+    <t>FELLT HAPPY</t>
   </si>
 </sst>
 </file>
@@ -384,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -428,9 +491,13 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -930,74 +997,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="22">
         <v>12625004</v>
       </c>
-      <c r="G2" s="21"/>
+      <c r="G2" s="22"/>
+      <c r="I2" s="19"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="21"/>
+      <c r="G3" s="22"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
     </row>
     <row r="5" spans="1:14" ht="42" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -1378,160 +1446,280 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13" t="s">
-        <v>65</v>
+      <c r="A14" s="13">
+        <v>46259</v>
       </c>
       <c r="B14" s="14">
-        <v>350</v>
+        <v>540</v>
       </c>
       <c r="C14" s="14">
         <v>30</v>
       </c>
       <c r="D14" s="14">
-        <v>240</v>
+        <v>350</v>
       </c>
       <c r="E14" s="14">
+        <v>60</v>
+      </c>
+      <c r="F14" s="14">
         <v>120</v>
       </c>
-      <c r="F14" s="14">
-        <v>350</v>
-      </c>
       <c r="G14" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H14" s="14">
         <v>120</v>
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>1210</v>
+        <v>1220</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="L14" s="16" t="s">
         <v>55</v>
       </c>
       <c r="M14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B15" s="14">
+        <v>540</v>
+      </c>
+      <c r="C15" s="14">
+        <v>30</v>
+      </c>
+      <c r="D15" s="14">
+        <v>240</v>
+      </c>
+      <c r="E15" s="14">
+        <v>60</v>
+      </c>
+      <c r="F15" s="14">
+        <v>350</v>
+      </c>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="14">
+        <v>120</v>
+      </c>
+      <c r="I15" s="15">
+        <f t="shared" si="0"/>
+        <v>1340</v>
+      </c>
+      <c r="J15" s="15">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B16" s="14">
+        <v>540</v>
+      </c>
+      <c r="C16" s="14">
+        <v>30</v>
+      </c>
+      <c r="D16" s="14">
+        <v>240</v>
+      </c>
+      <c r="E16" s="14">
+        <v>120</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>60</v>
+      </c>
+      <c r="I16" s="15">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J16" s="15">
+        <f t="shared" si="1"/>
+        <v>450</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N16" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="N14" s="17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+    </row>
+    <row r="17" spans="1:184" x14ac:dyDescent="0.35">
+      <c r="A17" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B17" s="14">
+        <v>480</v>
+      </c>
+      <c r="C17" s="14">
+        <v>60</v>
+      </c>
+      <c r="D17" s="14">
+        <v>180</v>
+      </c>
+      <c r="E17" s="14">
+        <v>70</v>
+      </c>
+      <c r="F17" s="14">
+        <v>110</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>120</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+        <v>420</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:184" x14ac:dyDescent="0.35">
+      <c r="A18" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B18" s="14">
+        <v>480</v>
+      </c>
+      <c r="C18" s="14">
+        <v>60</v>
+      </c>
+      <c r="D18" s="14">
+        <v>180</v>
+      </c>
+      <c r="E18" s="14">
+        <v>120</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>20</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
-    </row>
-    <row r="17" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+        <v>580</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:184" x14ac:dyDescent="0.35">
+      <c r="A19" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B19" s="14">
+        <v>480</v>
+      </c>
+      <c r="C19" s="14">
+        <v>60</v>
+      </c>
+      <c r="D19" s="14">
+        <v>180</v>
+      </c>
+      <c r="E19" s="14">
+        <v>60</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>60</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
-    </row>
-    <row r="18" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
-    </row>
-    <row r="19" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>600</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="20" spans="1:184" x14ac:dyDescent="0.35">
       <c r="A20" s="13"/>
@@ -1542,8 +1730,14 @@
       <c r="F20" s="13"/>
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
+      <c r="I20" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J20" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="K20" s="13"/>
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
@@ -1720,510 +1914,1031 @@
       <c r="GB20" s="13"/>
     </row>
     <row r="21" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="14">
+        <v>480</v>
+      </c>
+      <c r="C21" s="14">
+        <v>60</v>
+      </c>
+      <c r="D21" s="14">
+        <v>180</v>
+      </c>
+      <c r="E21" s="14">
+        <v>60</v>
+      </c>
+      <c r="F21" s="14">
+        <v>100</v>
+      </c>
+      <c r="G21" s="14">
+        <v>2</v>
+      </c>
+      <c r="H21" s="14">
+        <v>60</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="22" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B22" s="14">
+        <v>480</v>
+      </c>
+      <c r="C22" s="14">
+        <v>60</v>
+      </c>
+      <c r="D22" s="14">
+        <v>240</v>
+      </c>
+      <c r="E22" s="14">
+        <v>120</v>
+      </c>
+      <c r="F22" s="14">
+        <v>350</v>
+      </c>
+      <c r="G22" s="14">
+        <v>7</v>
+      </c>
+      <c r="H22" s="14">
+        <v>120</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
-    </row>
-    <row r="23" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+        <v>70</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:184" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B23" s="14">
+        <v>480</v>
+      </c>
+      <c r="C23" s="14">
+        <v>60</v>
+      </c>
+      <c r="D23" s="14">
+        <v>180</v>
+      </c>
+      <c r="E23" s="14">
+        <v>60</v>
+      </c>
+      <c r="F23" s="14">
+        <v>200</v>
+      </c>
+      <c r="G23" s="14">
+        <v>4</v>
+      </c>
+      <c r="H23" s="14">
+        <v>120</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
-    </row>
-    <row r="24" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+        <v>340</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:184" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B24" s="14">
+        <v>480</v>
+      </c>
+      <c r="C24" s="14">
+        <v>60</v>
+      </c>
+      <c r="D24" s="14">
+        <v>180</v>
+      </c>
+      <c r="E24" s="14">
+        <v>60</v>
+      </c>
+      <c r="F24" s="14">
+        <v>350</v>
+      </c>
+      <c r="G24" s="14">
+        <v>7</v>
+      </c>
+      <c r="H24" s="14">
+        <v>120</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>190</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="25" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B25" s="14">
+        <v>480</v>
+      </c>
+      <c r="C25" s="14">
+        <v>100</v>
+      </c>
+      <c r="D25" s="14">
+        <v>180</v>
+      </c>
+      <c r="E25" s="14">
+        <v>60</v>
+      </c>
+      <c r="F25" s="14">
+        <v>350</v>
+      </c>
+      <c r="G25" s="14">
+        <v>7</v>
+      </c>
+      <c r="H25" s="14">
+        <v>120</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="26" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B26" s="14">
+        <v>480</v>
+      </c>
+      <c r="C26" s="14">
+        <v>120</v>
+      </c>
+      <c r="D26" s="14">
+        <v>180</v>
+      </c>
+      <c r="E26" s="14">
+        <v>60</v>
+      </c>
+      <c r="F26" s="14">
+        <v>50</v>
+      </c>
+      <c r="G26" s="14">
+        <v>1</v>
+      </c>
+      <c r="H26" s="14">
+        <v>130</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="27" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B27" s="14">
+        <v>480</v>
+      </c>
+      <c r="C27" s="14">
+        <v>120</v>
+      </c>
+      <c r="D27" s="14">
+        <v>180</v>
+      </c>
+      <c r="E27" s="14">
+        <v>60</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <v>120</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="28" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B28" s="14">
+        <v>480</v>
+      </c>
+      <c r="C28" s="14">
+        <v>120</v>
+      </c>
+      <c r="D28" s="14">
+        <v>180</v>
+      </c>
+      <c r="E28" s="14">
+        <v>60</v>
+      </c>
+      <c r="F28" s="14">
+        <v>150</v>
+      </c>
+      <c r="G28" s="14">
+        <v>3</v>
+      </c>
+      <c r="H28" s="14">
+        <v>120</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J28" s="15">
+        <v>120</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:184" x14ac:dyDescent="0.35">
+      <c r="A29" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B29" s="14">
+        <v>480</v>
+      </c>
+      <c r="C29" s="14">
+        <v>120</v>
+      </c>
+      <c r="D29" s="14">
+        <v>180</v>
+      </c>
+      <c r="E29" s="14">
+        <v>120</v>
+      </c>
+      <c r="F29" s="14">
+        <v>350</v>
+      </c>
+      <c r="G29" s="14">
+        <v>7</v>
+      </c>
+      <c r="H29" s="14">
+        <v>120</v>
+      </c>
+      <c r="I29" s="15">
+        <f t="shared" si="0"/>
+        <v>1370</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
-    </row>
-    <row r="29" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+        <v>70</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:184" x14ac:dyDescent="0.35">
+      <c r="A30" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B30" s="14">
+        <v>480</v>
+      </c>
+      <c r="C30" s="14">
+        <v>120</v>
+      </c>
+      <c r="D30" s="14">
+        <v>180</v>
+      </c>
+      <c r="E30" s="14">
+        <v>120</v>
+      </c>
+      <c r="F30" s="14">
+        <v>200</v>
+      </c>
+      <c r="G30" s="14">
+        <v>4</v>
+      </c>
+      <c r="H30" s="14">
+        <v>120</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
-    </row>
-    <row r="30" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+        <v>220</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:184" x14ac:dyDescent="0.35">
+      <c r="A31" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B31" s="14">
+        <v>480</v>
+      </c>
+      <c r="C31" s="14">
+        <v>120</v>
+      </c>
+      <c r="D31" s="14">
+        <v>180</v>
+      </c>
+      <c r="E31" s="14">
+        <v>120</v>
+      </c>
+      <c r="F31" s="14">
+        <v>200</v>
+      </c>
+      <c r="G31" s="14">
+        <v>4</v>
+      </c>
+      <c r="H31" s="14">
+        <v>120</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
-    </row>
-    <row r="31" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+        <v>220</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:184" x14ac:dyDescent="0.35">
+      <c r="A32" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B32" s="14">
+        <v>480</v>
+      </c>
+      <c r="C32" s="14">
+        <v>120</v>
+      </c>
+      <c r="D32" s="14">
+        <v>180</v>
+      </c>
+      <c r="E32" s="14">
+        <v>120</v>
+      </c>
+      <c r="F32" s="14">
+        <v>200</v>
+      </c>
+      <c r="G32" s="14">
+        <v>4</v>
+      </c>
+      <c r="H32" s="14">
+        <v>120</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
-    </row>
-    <row r="32" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+        <v>220</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A33" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B33" s="14">
+        <v>480</v>
+      </c>
+      <c r="C33" s="14">
+        <v>120</v>
+      </c>
+      <c r="D33" s="14">
+        <v>240</v>
+      </c>
+      <c r="E33" s="14">
+        <v>120</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>150</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+        <v>330</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A34" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B34" s="14">
+        <v>300</v>
+      </c>
+      <c r="C34" s="14">
+        <v>120</v>
+      </c>
+      <c r="D34" s="14">
+        <v>180</v>
+      </c>
+      <c r="E34" s="14">
+        <v>120</v>
+      </c>
+      <c r="F34" s="14">
+        <v>100</v>
+      </c>
+      <c r="G34" s="14">
+        <v>2</v>
+      </c>
+      <c r="H34" s="14">
+        <v>120</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+        <v>500</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A35" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B35" s="14">
+        <v>300</v>
+      </c>
+      <c r="C35" s="14">
+        <v>120</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E35" s="14">
+        <v>120</v>
+      </c>
+      <c r="F35" s="14">
+        <v>100</v>
+      </c>
+      <c r="G35" s="14">
+        <v>2</v>
+      </c>
+      <c r="H35" s="14">
+        <v>120</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>760</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A36" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B36" s="14">
+        <v>220</v>
+      </c>
+      <c r="C36" s="14">
+        <v>20</v>
+      </c>
+      <c r="D36" s="14">
+        <v>180</v>
+      </c>
+      <c r="E36" s="14">
+        <v>30</v>
+      </c>
+      <c r="F36" s="14">
+        <v>350</v>
+      </c>
+      <c r="G36" s="14">
+        <v>7</v>
+      </c>
+      <c r="H36" s="14">
+        <v>120</v>
+      </c>
+      <c r="I36" s="15">
+        <f t="shared" ref="I36:I40" si="2">IF(SUM(B36:F36,H36)=0,"",SUM(B36:F36,H36))</f>
+        <v>920</v>
+      </c>
+      <c r="J36" s="15">
+        <f t="shared" ref="J36:J40" si="3">IF(I36="","",1440-I36)</f>
+        <v>520</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A37" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B37" s="14">
+        <v>300</v>
+      </c>
+      <c r="C37" s="14">
+        <v>30</v>
+      </c>
+      <c r="D37" s="14">
+        <v>150</v>
+      </c>
+      <c r="E37" s="14">
+        <v>30</v>
+      </c>
+      <c r="F37" s="14">
+        <v>200</v>
+      </c>
+      <c r="G37" s="14">
+        <v>4</v>
+      </c>
+      <c r="H37" s="14">
+        <v>120</v>
+      </c>
+      <c r="I37" s="15">
+        <f t="shared" si="2"/>
+        <v>830</v>
+      </c>
+      <c r="J37" s="15">
+        <f t="shared" si="3"/>
+        <v>610</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A38" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B38" s="14">
+        <v>240</v>
+      </c>
+      <c r="C38" s="14">
+        <v>30</v>
+      </c>
+      <c r="D38" s="14">
+        <v>240</v>
+      </c>
+      <c r="E38" s="14">
+        <v>30</v>
+      </c>
+      <c r="F38" s="14">
+        <v>300</v>
+      </c>
+      <c r="G38" s="14">
+        <v>5</v>
+      </c>
+      <c r="H38" s="14">
+        <v>150</v>
+      </c>
+      <c r="I38" s="15">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="J38" s="15">
+        <f t="shared" si="3"/>
+        <v>450</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A39" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B39" s="14">
+        <v>180</v>
+      </c>
+      <c r="C39" s="14">
+        <v>30</v>
+      </c>
+      <c r="D39" s="14">
+        <v>180</v>
+      </c>
+      <c r="E39" s="14">
+        <v>40</v>
+      </c>
+      <c r="F39" s="14">
+        <v>350</v>
+      </c>
+      <c r="G39" s="14">
+        <v>7</v>
+      </c>
+      <c r="H39" s="14">
+        <v>120</v>
+      </c>
+      <c r="I39" s="15">
+        <f t="shared" si="2"/>
+        <v>900</v>
+      </c>
+      <c r="J39" s="15">
+        <f t="shared" si="3"/>
+        <v>540</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A40" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B40" s="14">
+        <v>280</v>
+      </c>
+      <c r="C40" s="14">
+        <v>30</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E40" s="14">
+        <v>40</v>
+      </c>
+      <c r="F40" s="14">
+        <v>100</v>
+      </c>
+      <c r="G40" s="14">
+        <v>2</v>
+      </c>
+      <c r="H40" s="14">
+        <v>120</v>
+      </c>
+      <c r="I40" s="15">
+        <f t="shared" si="2"/>
+        <v>570</v>
+      </c>
+      <c r="J40" s="15">
+        <f t="shared" si="3"/>
+        <v>870</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A41" s="23"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
+      <c r="N41" s="17"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A42" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B42" s="14">
+        <v>280</v>
+      </c>
+      <c r="C42" s="14">
+        <v>0</v>
+      </c>
+      <c r="D42" s="14">
+        <v>120</v>
+      </c>
+      <c r="E42" s="14">
+        <v>40</v>
+      </c>
+      <c r="F42" s="14">
+        <v>0</v>
+      </c>
+      <c r="G42" s="14">
+        <v>0</v>
+      </c>
+      <c r="H42" s="14">
+        <v>120</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>560</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A43" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B43" s="14">
+        <v>280</v>
+      </c>
+      <c r="C43" s="14">
+        <v>120</v>
+      </c>
+      <c r="D43" s="14">
+        <v>120</v>
+      </c>
+      <c r="E43" s="14">
+        <v>60</v>
+      </c>
+      <c r="F43" s="14">
+        <v>100</v>
+      </c>
+      <c r="G43" s="14">
+        <v>2</v>
+      </c>
+      <c r="H43" s="14">
+        <v>120</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="13"/>
@@ -2807,11 +3522,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2829,11 +3544,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2851,11 +3566,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2873,11 +3588,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2895,11 +3610,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2917,11 +3632,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -2939,11 +3654,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -2961,11 +3676,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -2983,11 +3698,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3005,11 +3720,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3027,11 +3742,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3049,11 +3764,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3071,11 +3786,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3093,11 +3808,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3115,11 +3830,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3137,11 +3852,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3159,11 +3874,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3181,11 +3896,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3203,11 +3918,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3225,11 +3940,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3247,11 +3962,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3269,11 +3984,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3291,11 +4006,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3313,11 +4028,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3335,11 +4050,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3357,11 +4072,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3379,11 +4094,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3401,11 +4116,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3423,11 +4138,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3445,11 +4160,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3467,11 +4182,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3489,11 +4204,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3511,11 +4226,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3533,11 +4248,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3555,11 +4270,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3577,11 +4292,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3599,11 +4314,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3621,11 +4336,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3643,11 +4358,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3665,11 +4380,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3687,11 +4402,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3709,11 +4424,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3731,11 +4446,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3753,11 +4468,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3775,11 +4490,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3797,11 +4512,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3819,11 +4534,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3841,11 +4556,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3863,11 +4578,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3885,11 +4600,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3907,11 +4622,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -3929,11 +4644,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -3951,11 +4666,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -3973,11 +4688,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -3995,11 +4710,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4017,11 +4732,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4039,11 +4754,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4061,11 +4776,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4083,11 +4798,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4105,11 +4820,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4127,11 +4842,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4149,11 +4864,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4171,11 +4886,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4193,11 +4908,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4215,11 +4930,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4237,11 +4952,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4259,11 +4974,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4281,11 +4996,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4303,11 +5018,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4325,11 +5040,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4347,11 +5062,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4369,11 +5084,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4391,11 +5106,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4413,11 +5128,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4435,11 +5150,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4457,11 +5172,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4479,11 +5194,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4501,11 +5216,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4523,11 +5238,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4545,11 +5260,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4567,11 +5282,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4589,11 +5304,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4611,11 +5326,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4633,11 +5348,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4655,11 +5370,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4677,11 +5392,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4699,11 +5414,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4721,11 +5436,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4743,11 +5458,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4765,11 +5480,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4787,11 +5502,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4809,11 +5524,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4831,11 +5546,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4853,11 +5568,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4875,11 +5590,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4897,11 +5612,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4919,11 +5634,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -4941,11 +5656,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -4963,11 +5678,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -4985,11 +5700,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5007,11 +5722,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5029,11 +5744,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5051,11 +5766,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5073,11 +5788,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5095,11 +5810,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5117,11 +5832,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5139,11 +5854,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5161,11 +5876,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5183,11 +5898,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5205,11 +5920,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5227,11 +5942,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5249,11 +5964,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5271,11 +5986,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5293,11 +6008,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5315,11 +6030,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5337,11 +6052,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5359,11 +6074,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5381,11 +6096,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5403,11 +6118,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5425,11 +6140,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5447,11 +6162,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5469,11 +6184,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5491,11 +6206,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5513,11 +6228,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5535,11 +6250,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5557,11 +6272,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5579,11 +6294,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5601,11 +6316,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5623,11 +6338,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5645,11 +6360,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5667,11 +6382,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5689,11 +6404,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5711,11 +6426,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5733,11 +6448,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5755,11 +6470,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5777,11 +6492,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5799,11 +6514,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5821,11 +6536,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5843,11 +6558,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5865,11 +6580,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5887,11 +6602,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5909,11 +6624,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -5931,11 +6646,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -5953,11 +6668,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -5975,11 +6690,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -5997,11 +6712,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6019,11 +6734,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6041,11 +6756,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6063,11 +6778,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6085,11 +6800,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6107,11 +6822,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6129,11 +6844,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6151,11 +6866,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6173,11 +6888,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6195,11 +6910,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6217,11 +6932,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6239,11 +6954,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6261,11 +6976,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6283,11 +6998,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6305,11 +7020,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6327,11 +7042,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6349,11 +7064,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6371,11 +7086,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6393,11 +7108,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6415,11 +7130,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6437,11 +7152,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6459,11 +7174,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6481,11 +7196,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6503,11 +7218,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6525,11 +7240,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6547,11 +7262,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6569,11 +7284,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6591,11 +7306,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6613,11 +7328,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6635,11 +7350,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6657,11 +7372,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6679,11 +7394,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6701,11 +7416,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6723,11 +7438,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6745,11 +7460,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6767,11 +7482,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6789,11 +7504,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6811,11 +7526,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6833,11 +7548,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6855,11 +7570,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6877,11 +7592,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6899,11 +7614,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6921,11 +7636,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -6943,11 +7658,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -6965,11 +7680,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -6987,11 +7702,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7009,11 +7724,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7031,11 +7746,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7053,11 +7768,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7075,11 +7790,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7097,11 +7812,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7119,11 +7834,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7141,11 +7856,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7163,11 +7878,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7185,11 +7900,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7207,11 +7922,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7229,11 +7944,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7251,11 +7966,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7273,11 +7988,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7295,11 +8010,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7317,11 +8032,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7339,11 +8054,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7361,11 +8076,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7383,11 +8098,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7405,11 +8120,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7427,11 +8142,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7449,11 +8164,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7471,11 +8186,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7493,11 +8208,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7515,11 +8230,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7537,11 +8252,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7559,11 +8274,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7581,11 +8296,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7603,11 +8318,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7625,11 +8340,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7647,11 +8362,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7669,11 +8384,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7691,11 +8406,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7713,11 +8428,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7735,11 +8450,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7757,11 +8472,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7779,11 +8494,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7801,11 +8516,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7823,11 +8538,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7845,11 +8560,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7867,11 +8582,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7889,11 +8604,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7911,11 +8626,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -7933,11 +8648,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -7955,11 +8670,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -7977,11 +8692,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -7999,11 +8714,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8021,11 +8736,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8043,11 +8758,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8065,11 +8780,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8087,11 +8802,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8109,11 +8824,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8131,11 +8846,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8153,11 +8868,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8175,11 +8890,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8197,11 +8912,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8219,11 +8934,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8241,11 +8956,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8263,11 +8978,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8285,11 +9000,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8307,11 +9022,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8329,11 +9044,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8351,11 +9066,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8373,11 +9088,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8395,11 +9110,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8417,11 +9132,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8439,11 +9154,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8461,11 +9176,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8483,11 +9198,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8505,11 +9220,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8527,11 +9242,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8549,11 +9264,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8571,11 +9286,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8593,11 +9308,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8615,11 +9330,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8637,11 +9352,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8659,11 +9374,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8681,11 +9396,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8703,11 +9418,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8725,11 +9440,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8747,11 +9462,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8769,11 +9484,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8791,11 +9506,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8813,11 +9528,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8835,11 +9550,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8857,11 +9572,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8879,11 +9594,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8901,11 +9616,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8923,11 +9638,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -8945,11 +9660,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -8967,11 +9682,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -8989,11 +9704,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9011,11 +9726,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9033,11 +9748,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9055,11 +9770,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9077,11 +9792,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9099,11 +9814,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9121,11 +9836,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9143,11 +9858,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9165,11 +9880,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9187,11 +9902,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9209,11 +9924,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9231,11 +9946,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9253,11 +9968,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9275,11 +9990,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9297,11 +10012,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9319,11 +10034,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9341,11 +10056,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9363,11 +10078,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9385,11 +10100,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9407,11 +10122,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9429,11 +10144,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9451,11 +10166,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9473,11 +10188,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9495,11 +10210,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9517,11 +10232,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9539,11 +10254,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9561,11 +10276,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9583,11 +10298,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9605,11 +10320,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9627,11 +10342,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9649,11 +10364,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9671,11 +10386,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9693,11 +10408,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9715,11 +10430,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9737,11 +10452,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9759,11 +10474,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9781,11 +10496,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9803,11 +10518,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9825,11 +10540,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9847,11 +10562,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="15">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9869,11 +10584,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9891,11 +10606,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9913,11 +10628,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -9935,11 +10650,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -9957,11 +10672,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -9979,11 +10694,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10001,11 +10716,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10023,11 +10738,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10045,11 +10760,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10067,11 +10782,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10089,11 +10804,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K401" s="16"/>
@@ -10115,26 +10830,26 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J21:J401">
+  <conditionalFormatting sqref="J21:J40 J42:J401">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K21:K401 K6:K19" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K19 K21:K40 K42:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L21:L401 L6:L19" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L19 L21:L40 L42:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M21:M401 M6:M19" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M19 M21:M40 M42:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>